--- a/5_Judgemental_Nowcasts_Derivations_Analysis/0_Main_Analysis/EDA_Tables/Nowcast_Series_Full_GDP.xlsx
+++ b/5_Judgemental_Nowcasts_Derivations_Analysis/0_Main_Analysis/EDA_Tables/Nowcast_Series_Full_GDP.xlsx
@@ -750,7 +750,7 @@
         <v>0.444900743380838</v>
       </c>
       <c r="E2">
-        <v>0.5984434428180319</v>
+        <v>0.5278817260644753</v>
       </c>
       <c r="F2">
         <v>0.6980161645848688</v>
@@ -768,7 +768,7 @@
         <v>0.08010366175749883</v>
       </c>
       <c r="K2">
-        <v>0.2336463611946927</v>
+        <v>0.1630846444411361</v>
       </c>
       <c r="L2">
         <v>0.3332190829615296</v>
@@ -783,7 +783,7 @@
         <v>0.355099256619162</v>
       </c>
       <c r="P2">
-        <v>0.2015565571819682</v>
+        <v>0.2721182739355248</v>
       </c>
       <c r="Q2">
         <v>0.1019838354151312</v>
@@ -846,7 +846,7 @@
         <v>-0.2846934198658403</v>
       </c>
       <c r="AK2">
-        <v>-0.1311507204286465</v>
+        <v>-0.2017124371822031</v>
       </c>
       <c r="AL2">
         <v>-0.03157799866180955</v>
@@ -861,7 +861,7 @@
         <v>-0.009697825004177152</v>
       </c>
       <c r="AP2">
-        <v>-0.163240524441371</v>
+        <v>-0.09267880768781439</v>
       </c>
       <c r="AQ2">
         <v>-0.262813246208208</v>
@@ -932,7 +932,7 @@
         <v>0.352879089972535</v>
       </c>
       <c r="E3">
-        <v>0.5698310446372115</v>
+        <v>0.8158350159267664</v>
       </c>
       <c r="F3">
         <v>1.499182264219509</v>
@@ -950,7 +950,7 @@
         <v>0.233656786230793</v>
       </c>
       <c r="K3">
-        <v>0.4506087408954694</v>
+        <v>0.6966127121850244</v>
       </c>
       <c r="L3">
         <v>1.379959960477767</v>
@@ -965,7 +965,7 @@
         <v>0.04712091002746505</v>
       </c>
       <c r="P3">
-        <v>-0.1698310446372114</v>
+        <v>-0.4158350159267664</v>
       </c>
       <c r="Q3">
         <v>-1.099182264219509</v>
@@ -1028,7 +1028,7 @@
         <v>0.114434482489051</v>
       </c>
       <c r="AK3">
-        <v>0.3313864371537274</v>
+        <v>0.5773904084432824</v>
       </c>
       <c r="AL3">
         <v>1.260737656736025</v>
@@ -1043,7 +1043,7 @@
         <v>-0.07210139371427696</v>
       </c>
       <c r="AP3">
-        <v>-0.2890533483789535</v>
+        <v>-0.5350573196685084</v>
       </c>
       <c r="AQ3">
         <v>-1.218404567961251</v>
@@ -1114,7 +1114,7 @@
         <v>0.231784144206971</v>
       </c>
       <c r="E4">
-        <v>0.4888361074519135</v>
+        <v>0.4070688708672613</v>
       </c>
       <c r="F4">
         <v>0.5030181086519089</v>
@@ -1132,7 +1132,7 @@
         <v>0.4136519263293706</v>
       </c>
       <c r="K4">
-        <v>0.6707038895743132</v>
+        <v>0.5889366529896609</v>
       </c>
       <c r="L4">
         <v>0.6848858907743085</v>
@@ -1147,7 +1147,7 @@
         <v>-0.431784144206971</v>
       </c>
       <c r="P4">
-        <v>-0.6888361074519136</v>
+        <v>-0.6070688708672614</v>
       </c>
       <c r="Q4">
         <v>-0.7030181086519089</v>
@@ -1210,7 +1210,7 @@
         <v>0.5955197084517702</v>
       </c>
       <c r="AK4">
-        <v>0.8525716716967128</v>
+        <v>0.7708044351120605</v>
       </c>
       <c r="AL4">
         <v>0.8667536728967081</v>
@@ -1225,7 +1225,7 @@
         <v>-0.2499163620845714</v>
       </c>
       <c r="AP4">
-        <v>-0.506968325329514</v>
+        <v>-0.4252010887448617</v>
       </c>
       <c r="AQ4">
         <v>-0.5211503265295093</v>
@@ -1296,7 +1296,7 @@
         <v>-0.137004828987682</v>
       </c>
       <c r="E5">
-        <v>0.4640669336751295</v>
+        <v>0.4060566115363017</v>
       </c>
       <c r="F5">
         <v>0.5101576022592715</v>
@@ -1314,7 +1314,7 @@
         <v>-0.4077140872443247</v>
       </c>
       <c r="K5">
-        <v>0.1933576754184868</v>
+        <v>0.135347353279659</v>
       </c>
       <c r="L5">
         <v>0.2394483440026288</v>
@@ -1329,7 +1329,7 @@
         <v>0.237004828987682</v>
       </c>
       <c r="P5">
-        <v>-0.3640669336751295</v>
+        <v>-0.3060566115363017</v>
       </c>
       <c r="Q5">
         <v>-0.4101576022592716</v>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="Y5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="b">
         <v>1</v>
@@ -1392,7 +1392,7 @@
         <v>-0.6784233455009674</v>
       </c>
       <c r="AK5">
-        <v>-0.07735158283815591</v>
+        <v>-0.1353619049769837</v>
       </c>
       <c r="AL5">
         <v>-0.03126091425401389</v>
@@ -1407,7 +1407,7 @@
         <v>-0.03370442926896072</v>
       </c>
       <c r="AP5">
-        <v>-0.6347761919317723</v>
+        <v>-0.5767658697929444</v>
       </c>
       <c r="AQ5">
         <v>-0.6808668605159143</v>
@@ -1434,7 +1434,7 @@
         <v>0.7292907417433573</v>
       </c>
       <c r="AY5">
-        <v>0.7292907417433573</v>
+        <v>-0.2707092582566427</v>
       </c>
       <c r="AZ5">
         <v>0.7292907417433573</v>
@@ -1478,7 +1478,7 @@
         <v>-0.09251056768275739</v>
       </c>
       <c r="E6">
-        <v>0.4589753847598654</v>
+        <v>0.2658412787400625</v>
       </c>
       <c r="F6">
         <v>0.233981281497472</v>
@@ -1496,7 +1496,7 @@
         <v>0.5000022252070861</v>
       </c>
       <c r="K6">
-        <v>1.051488177649709</v>
+        <v>0.8583540716299061</v>
       </c>
       <c r="L6">
         <v>0.8264940743873155</v>
@@ -1511,7 +1511,7 @@
         <v>-0.2074894323172426</v>
       </c>
       <c r="P6">
-        <v>-0.7589753847598654</v>
+        <v>-0.5658412787400625</v>
       </c>
       <c r="Q6">
         <v>-0.533981281497472</v>
@@ -1574,7 +1574,7 @@
         <v>1.09251501809693</v>
       </c>
       <c r="AK6">
-        <v>1.644000970539552</v>
+        <v>1.45086686451975</v>
       </c>
       <c r="AL6">
         <v>1.419006867277159</v>
@@ -1589,7 +1589,7 @@
         <v>0.3850233605726009</v>
       </c>
       <c r="AP6">
-        <v>-0.1664625918700219</v>
+        <v>0.02667151414978097</v>
       </c>
       <c r="AQ6">
         <v>0.05853151139237145</v>
@@ -1660,7 +1660,7 @@
         <v>0.535895844045383</v>
       </c>
       <c r="E7">
-        <v>0.3811469122973433</v>
+        <v>0.1668148420067005</v>
       </c>
       <c r="F7">
         <v>0.06328541723172172</v>
@@ -1678,7 +1678,7 @@
         <v>-0.1855398129119595</v>
       </c>
       <c r="K7">
-        <v>-0.3402887446599993</v>
+        <v>-0.5546208149506421</v>
       </c>
       <c r="L7">
         <v>-0.6581502397256208</v>
@@ -1693,7 +1693,7 @@
         <v>0.3641041559546084</v>
       </c>
       <c r="P7">
-        <v>0.5188530877026482</v>
+        <v>0.733185157993291</v>
       </c>
       <c r="Q7">
         <v>0.8367145827682697</v>
@@ -1756,7 +1756,7 @@
         <v>-0.9069754698693021</v>
       </c>
       <c r="AK7">
-        <v>-1.061724401617342</v>
+        <v>-1.276056471907985</v>
       </c>
       <c r="AL7">
         <v>-1.379585896682963</v>
@@ -1771,7 +1771,7 @@
         <v>-0.3573315010027341</v>
       </c>
       <c r="AP7">
-        <v>-0.2025825692546944</v>
+        <v>0.01174950103594841</v>
       </c>
       <c r="AQ7">
         <v>0.1152789258109271</v>
@@ -1842,7 +1842,7 @@
         <v>0.336410475895099</v>
       </c>
       <c r="E8">
-        <v>0.4852206541758703</v>
+        <v>0.3071481657186778</v>
       </c>
       <c r="F8">
         <v>0.3223207091055595</v>
@@ -1860,7 +1860,7 @@
         <v>-0.0473467753320379</v>
       </c>
       <c r="K8">
-        <v>0.1014634029487334</v>
+        <v>-0.07660908550845907</v>
       </c>
       <c r="L8">
         <v>-0.0614365421215774</v>
@@ -1875,7 +1875,7 @@
         <v>-0.03641047589509899</v>
       </c>
       <c r="P8">
-        <v>-0.1852206541758703</v>
+        <v>-0.007148165718677824</v>
       </c>
       <c r="Q8">
         <v>-0.0223207091055595</v>
@@ -1896,13 +1896,13 @@
         <v>0</v>
       </c>
       <c r="W8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
       <c r="Y8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
@@ -1938,7 +1938,7 @@
         <v>-0.4311040265591748</v>
       </c>
       <c r="AK8">
-        <v>-0.2822938482784035</v>
+        <v>-0.460366336735596</v>
       </c>
       <c r="AL8">
         <v>-0.4451937933487143</v>
@@ -1953,7 +1953,7 @@
         <v>-0.4201677271222359</v>
       </c>
       <c r="AP8">
-        <v>-0.5689779054030072</v>
+        <v>-0.3909054169458147</v>
       </c>
       <c r="AQ8">
         <v>-0.4060779603326964</v>
@@ -1974,13 +1974,13 @@
         <v>-0.3837572512271369</v>
       </c>
       <c r="AW8">
-        <v>0.6162427487728631</v>
+        <v>-0.3837572512271369</v>
       </c>
       <c r="AX8">
         <v>0.6162427487728631</v>
       </c>
       <c r="AY8">
-        <v>0.6162427487728631</v>
+        <v>-0.3837572512271369</v>
       </c>
       <c r="AZ8">
         <v>-0.3837572512271369</v>
@@ -2024,7 +2024,7 @@
         <v>0.0917580682271779</v>
       </c>
       <c r="E9">
-        <v>0.5129871263628406</v>
+        <v>0.5498874657267171</v>
       </c>
       <c r="F9">
         <v>0.8179231863442404</v>
@@ -2042,7 +2042,7 @@
         <v>0.2526362739620144</v>
       </c>
       <c r="K9">
-        <v>0.6738653320976771</v>
+        <v>0.7107656714615536</v>
       </c>
       <c r="L9">
         <v>0.9788013920790769</v>
@@ -2057,7 +2057,7 @@
         <v>0.208241931772805</v>
       </c>
       <c r="P9">
-        <v>-0.2129871263628577</v>
+        <v>-0.2498874657267342</v>
       </c>
       <c r="Q9">
         <v>-0.5179231863442575</v>
@@ -2120,7 +2120,7 @@
         <v>0.4135144796968508</v>
       </c>
       <c r="AK9">
-        <v>0.8347435378325135</v>
+        <v>0.87164387719639</v>
       </c>
       <c r="AL9">
         <v>1.139679597813913</v>
@@ -2135,7 +2135,7 @@
         <v>0.3691201375076415</v>
       </c>
       <c r="AP9">
-        <v>-0.05210892062802122</v>
+        <v>-0.08900925999189771</v>
       </c>
       <c r="AQ9">
         <v>-0.357044980609421</v>
@@ -2206,7 +2206,7 @@
         <v>0.406193507823847</v>
       </c>
       <c r="E10">
-        <v>0.3987129603527378</v>
+        <v>0.1736804633958236</v>
       </c>
       <c r="F10">
         <v>0.06623769871308968</v>
@@ -2224,7 +2224,7 @@
         <v>-0.2935039203153312</v>
       </c>
       <c r="K10">
-        <v>-0.3009844677864404</v>
+        <v>-0.5260169647433546</v>
       </c>
       <c r="L10">
         <v>-0.6334597294260885</v>
@@ -2239,7 +2239,7 @@
         <v>-0.2061935078238442</v>
       </c>
       <c r="P10">
-        <v>-0.198712960352735</v>
+        <v>0.02631953660417918</v>
       </c>
       <c r="Q10">
         <v>0.1337623012869131</v>
@@ -2263,10 +2263,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
@@ -2302,7 +2302,7 @@
         <v>-0.9932013484545095</v>
       </c>
       <c r="AK10">
-        <v>-1.000681895925619</v>
+        <v>-1.225714392882533</v>
       </c>
       <c r="AL10">
         <v>-1.333157157565267</v>
@@ -2317,7 +2317,7 @@
         <v>-0.9058909359630225</v>
       </c>
       <c r="AP10">
-        <v>-0.8984103884919132</v>
+        <v>-0.6733778915349991</v>
       </c>
       <c r="AQ10">
         <v>-0.5659351268522651</v>
@@ -2341,10 +2341,10 @@
         <v>-0.6996974281391782</v>
       </c>
       <c r="AX10">
+        <v>-0.6996974281391782</v>
+      </c>
+      <c r="AY10">
         <v>0.3003025718608218</v>
-      </c>
-      <c r="AY10">
-        <v>-0.6996974281391782</v>
       </c>
       <c r="AZ10">
         <v>-0.6996974281391782</v>
@@ -2388,7 +2388,7 @@
         <v>0.480124956126704</v>
       </c>
       <c r="E11">
-        <v>0.4704147728506033</v>
+        <v>0.3086271608792364</v>
       </c>
       <c r="F11">
         <v>0.2723004694835739</v>
@@ -2406,7 +2406,7 @@
         <v>0.04148753195498317</v>
       </c>
       <c r="K11">
-        <v>0.03177734867888249</v>
+        <v>-0.1300102632924844</v>
       </c>
       <c r="L11">
         <v>-0.1663369546881469</v>
@@ -2421,7 +2421,7 @@
         <v>0.1398750438733006</v>
       </c>
       <c r="P11">
-        <v>0.1495852271494013</v>
+        <v>0.3113728391207681</v>
       </c>
       <c r="Q11">
         <v>0.3476995305164307</v>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="W11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="b">
         <v>0</v>
@@ -2484,7 +2484,7 @@
         <v>-0.3971498922167376</v>
       </c>
       <c r="AK11">
-        <v>-0.4068600754928383</v>
+        <v>-0.5686476874642052</v>
       </c>
       <c r="AL11">
         <v>-0.6049743788598677</v>
@@ -2499,7 +2499,7 @@
         <v>-0.2987623802984202</v>
       </c>
       <c r="AP11">
-        <v>-0.2890521970223195</v>
+        <v>-0.1272645850509527</v>
       </c>
       <c r="AQ11">
         <v>-0.09093789365529015</v>
@@ -2520,7 +2520,7 @@
         <v>-0.4386374241717208</v>
       </c>
       <c r="AW11">
-        <v>0.5613625758282792</v>
+        <v>-0.4386374241717208</v>
       </c>
       <c r="AX11">
         <v>-0.4386374241717208</v>
@@ -2570,7 +2570,7 @@
         <v>0.395376664579939</v>
       </c>
       <c r="E12">
-        <v>0.45960676335203</v>
+        <v>0.3194721332081325</v>
       </c>
       <c r="F12">
         <v>0.315926407730895</v>
@@ -2588,7 +2588,7 @@
         <v>0.1266839934041843</v>
       </c>
       <c r="K12">
-        <v>0.1909140921762753</v>
+        <v>0.05077946203237782</v>
       </c>
       <c r="L12">
         <v>0.04723373655514029</v>
@@ -2603,7 +2603,7 @@
         <v>0.07462333542005994</v>
       </c>
       <c r="P12">
-        <v>0.01039323664796893</v>
+        <v>0.1505278667918664</v>
       </c>
       <c r="Q12">
         <v>0.1540735922691039</v>
@@ -2666,7 +2666,7 @@
         <v>-0.1420086777715704</v>
       </c>
       <c r="AK12">
-        <v>-0.07777857899947938</v>
+        <v>-0.2179132091433769</v>
       </c>
       <c r="AL12">
         <v>-0.2214589346206144</v>
@@ -2681,7 +2681,7 @@
         <v>-0.1940693357556947</v>
       </c>
       <c r="AP12">
-        <v>-0.2582994345277858</v>
+        <v>-0.1181648043838883</v>
       </c>
       <c r="AQ12">
         <v>-0.1146190789066507</v>
@@ -2752,7 +2752,7 @@
         <v>0.350906646240513</v>
       </c>
       <c r="E13">
-        <v>0.4866309068941742</v>
+        <v>0.4935538258476527</v>
       </c>
       <c r="F13">
         <v>0.6653114026982063</v>
@@ -2770,7 +2770,7 @@
         <v>-0.06035272133397324</v>
       </c>
       <c r="K13">
-        <v>0.07537153931968799</v>
+        <v>0.0822944582731665</v>
       </c>
       <c r="L13">
         <v>0.2540520351237201</v>
@@ -2785,7 +2785,7 @@
         <v>-0.01090664624050958</v>
       </c>
       <c r="P13">
-        <v>-0.1466309068941708</v>
+        <v>-0.1535538258476493</v>
       </c>
       <c r="Q13">
         <v>-0.3253114026982029</v>
@@ -2848,7 +2848,7 @@
         <v>-0.4716120889084595</v>
       </c>
       <c r="AK13">
-        <v>-0.3358878282547982</v>
+        <v>-0.3289649093013197</v>
       </c>
       <c r="AL13">
         <v>-0.1572073324507661</v>
@@ -2863,7 +2863,7 @@
         <v>-0.4221660138149958</v>
       </c>
       <c r="AP13">
-        <v>-0.557890274468657</v>
+        <v>-0.5648131934221355</v>
       </c>
       <c r="AQ13">
         <v>-0.7365707702726891</v>
@@ -2934,7 +2934,7 @@
         <v>1.12101181637889</v>
       </c>
       <c r="E14">
-        <v>0.4459418294680377</v>
+        <v>0.2854538301566019</v>
       </c>
       <c r="F14">
         <v>0.1911349777009136</v>
@@ -2952,7 +2952,7 @@
         <v>0.6940883900913082</v>
       </c>
       <c r="K14">
-        <v>0.01901840318045589</v>
+        <v>-0.1414695961309799</v>
       </c>
       <c r="L14">
         <v>-0.2357884485866682</v>
@@ -2967,7 +2967,7 @@
         <v>-0.6710118163789014</v>
       </c>
       <c r="P14">
-        <v>0.0040581705319509</v>
+        <v>0.1645461698433867</v>
       </c>
       <c r="Q14">
         <v>0.258865022299075</v>
@@ -2988,13 +2988,13 @@
         <v>1</v>
       </c>
       <c r="W14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="b">
         <v>0</v>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
@@ -3030,7 +3030,7 @@
         <v>0.2671649638037264</v>
       </c>
       <c r="AK14">
-        <v>-0.4079050231071259</v>
+        <v>-0.5683930224185616</v>
       </c>
       <c r="AL14">
         <v>-0.66271187487425</v>
@@ -3045,7 +3045,7 @@
         <v>-1.097935242666483</v>
       </c>
       <c r="AP14">
-        <v>-0.4228652557556309</v>
+        <v>-0.2623772564441951</v>
       </c>
       <c r="AQ14">
         <v>-0.1680584039885068</v>
@@ -3066,13 +3066,13 @@
         <v>0.5730765737124182</v>
       </c>
       <c r="AW14">
-        <v>0.5730765737124182</v>
+        <v>-0.4269234262875818</v>
       </c>
       <c r="AX14">
         <v>-0.4269234262875818</v>
       </c>
       <c r="AY14">
-        <v>-0.4269234262875818</v>
+        <v>0.5730765737124182</v>
       </c>
       <c r="AZ14">
         <v>-0.4269234262875818</v>
@@ -3116,7 +3116,7 @@
         <v>0.809577098583235</v>
       </c>
       <c r="E15">
-        <v>0.4898183955613777</v>
+        <v>0.4880370991768954</v>
       </c>
       <c r="F15">
         <v>0.6058961837583665</v>
@@ -3134,7 +3134,7 @@
         <v>0.1931203845655475</v>
       </c>
       <c r="K15">
-        <v>-0.1266383184563099</v>
+        <v>-0.1284196148407921</v>
       </c>
       <c r="L15">
         <v>-0.01056053025932102</v>
@@ -3149,7 +3149,7 @@
         <v>-0.1095770985832464</v>
       </c>
       <c r="P15">
-        <v>0.2101816044386109</v>
+        <v>0.2119629008230932</v>
       </c>
       <c r="Q15">
         <v>0.09410381624162212</v>
@@ -3212,7 +3212,7 @@
         <v>-0.4233363294521401</v>
       </c>
       <c r="AK15">
-        <v>-0.7430950324739973</v>
+        <v>-0.7448763288584797</v>
       </c>
       <c r="AL15">
         <v>-0.6270172442770086</v>
@@ -3227,7 +3227,7 @@
         <v>-0.7260338126009339</v>
       </c>
       <c r="AP15">
-        <v>-0.4062751095790766</v>
+        <v>-0.4044938131945943</v>
       </c>
       <c r="AQ15">
         <v>-0.5223528977760654</v>
@@ -3298,7 +3298,7 @@
         <v>0.515056337211413</v>
       </c>
       <c r="E16">
-        <v>0.5308500955697427</v>
+        <v>0.5892375486112547</v>
       </c>
       <c r="F16">
         <v>0.8241758241758176</v>
@@ -3316,7 +3316,7 @@
         <v>-0.09191058748949987</v>
       </c>
       <c r="K16">
-        <v>-0.07611682913117013</v>
+        <v>-0.01772937608965819</v>
       </c>
       <c r="L16">
         <v>0.2172088994749047</v>
@@ -3331,7 +3331,7 @@
         <v>0.0349436627885984</v>
       </c>
       <c r="P16">
-        <v>0.01914990443026865</v>
+        <v>-0.03923754861124329</v>
       </c>
       <c r="Q16">
         <v>-0.2741758241758062</v>
@@ -3355,10 +3355,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="b">
         <v>1</v>
@@ -3394,7 +3394,7 @@
         <v>-0.6988775121904127</v>
       </c>
       <c r="AK16">
-        <v>-0.683083753832083</v>
+        <v>-0.624696300790571</v>
       </c>
       <c r="AL16">
         <v>-0.3897580252260081</v>
@@ -3409,7 +3409,7 @@
         <v>-0.5720232619123145</v>
       </c>
       <c r="AP16">
-        <v>-0.5878170202706442</v>
+        <v>-0.6462044733121561</v>
       </c>
       <c r="AQ16">
         <v>-0.8811427488767191</v>
@@ -3433,10 +3433,10 @@
         <v>-0.6069669247009128</v>
       </c>
       <c r="AX16">
+        <v>0.3930330752990872</v>
+      </c>
+      <c r="AY16">
         <v>-0.6069669247009128</v>
-      </c>
-      <c r="AY16">
-        <v>0.3930330752990872</v>
       </c>
       <c r="AZ16">
         <v>0.3930330752990872</v>
@@ -3480,7 +3480,7 @@
         <v>0.541582629209194</v>
       </c>
       <c r="E17">
-        <v>0.5146509551248899</v>
+        <v>0.498268675818354</v>
       </c>
       <c r="F17">
         <v>0.6069669247009128</v>
@@ -3498,7 +3498,7 @@
         <v>0.2443018737663426</v>
       </c>
       <c r="K17">
-        <v>0.2173701996820385</v>
+        <v>0.2009879203755026</v>
       </c>
       <c r="L17">
         <v>0.3096861692580615</v>
@@ -3513,7 +3513,7 @@
         <v>0.1584173707907947</v>
       </c>
       <c r="P17">
-        <v>0.1853490448750987</v>
+        <v>0.2017313241816346</v>
       </c>
       <c r="Q17">
         <v>0.09303307529907578</v>
@@ -3576,7 +3576,7 @@
         <v>-0.05297888167650877</v>
       </c>
       <c r="AK17">
-        <v>-0.07991055576081285</v>
+        <v>-0.09629283506734876</v>
       </c>
       <c r="AL17">
         <v>0.0124054138152101</v>
@@ -3591,7 +3591,7 @@
         <v>-0.1388633846520567</v>
       </c>
       <c r="AP17">
-        <v>-0.1119317105677526</v>
+        <v>-0.09554943126121673</v>
       </c>
       <c r="AQ17">
         <v>-0.2042476801437756</v>
@@ -3662,7 +3662,7 @@
         <v>-0.138856201462895</v>
       </c>
       <c r="E18">
-        <v>0.4741444152223665</v>
+        <v>0.3409278159840826</v>
       </c>
       <c r="F18">
         <v>0.2972807554428514</v>
@@ -3680,7 +3680,7 @@
         <v>-0.5904410907377504</v>
       </c>
       <c r="K18">
-        <v>0.02255952594751109</v>
+        <v>-0.1106570732907728</v>
       </c>
       <c r="L18">
         <v>-0.154304133832004</v>
@@ -3695,7 +3695,7 @@
         <v>0.4388562014628779</v>
       </c>
       <c r="P18">
-        <v>-0.1741444152223836</v>
+        <v>-0.04092781598409972</v>
       </c>
       <c r="Q18">
         <v>0.002719244557131517</v>
@@ -3716,7 +3716,7 @@
         <v>1</v>
       </c>
       <c r="W18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
@@ -3758,7 +3758,7 @@
         <v>-1.042025980012606</v>
       </c>
       <c r="AK18">
-        <v>-0.4290253633273443</v>
+        <v>-0.5622419625656282</v>
       </c>
       <c r="AL18">
         <v>-0.6058890231068594</v>
@@ -3773,7 +3773,7 @@
         <v>-0.0127286878119775</v>
       </c>
       <c r="AP18">
-        <v>-0.625729304497239</v>
+        <v>-0.4925127052589551</v>
       </c>
       <c r="AQ18">
         <v>-0.4488656447177239</v>
@@ -3794,7 +3794,7 @@
         <v>0.5484151107251446</v>
       </c>
       <c r="AW18">
-        <v>0.5484151107251446</v>
+        <v>-0.4515848892748554</v>
       </c>
       <c r="AX18">
         <v>0.5484151107251446</v>
@@ -3844,7 +3844,7 @@
         <v>0.0503775864399945</v>
       </c>
       <c r="E19">
-        <v>0.4777870639207178</v>
+        <v>0.3924672903298065</v>
       </c>
       <c r="F19">
         <v>0.4515848892748554</v>
@@ -3862,7 +3862,7 @@
         <v>0.2492191183843223</v>
       </c>
       <c r="K19">
-        <v>0.6766285958650455</v>
+        <v>0.5913088222741343</v>
       </c>
       <c r="L19">
         <v>0.6504264212191833</v>
@@ -3877,7 +3877,7 @@
         <v>0.4496224135599771</v>
       </c>
       <c r="P19">
-        <v>0.02221293607925379</v>
+        <v>0.1075327096701651</v>
       </c>
       <c r="Q19">
         <v>0.04841511072511617</v>
@@ -3940,7 +3940,7 @@
         <v>0.4480606503286501</v>
       </c>
       <c r="AK19">
-        <v>0.8754701278093733</v>
+        <v>0.790150354218462</v>
       </c>
       <c r="AL19">
         <v>0.849267953163511</v>
@@ -3955,7 +3955,7 @@
         <v>0.6484639455043049</v>
       </c>
       <c r="AP19">
-        <v>0.2210544680235816</v>
+        <v>0.3063742416144929</v>
       </c>
       <c r="AQ19">
         <v>0.247256642669444</v>
@@ -4026,7 +4026,7 @@
         <v>0.24747400421905</v>
       </c>
       <c r="E20">
-        <v>0.4138185309876257</v>
+        <v>0.1122805722851697</v>
       </c>
       <c r="F20">
         <v>-0.1988415319443278</v>
@@ -4044,7 +4044,7 @@
         <v>0.2301504875451686</v>
       </c>
       <c r="K20">
-        <v>0.3964950143137443</v>
+        <v>0.09495705561128835</v>
       </c>
       <c r="L20">
         <v>-0.2161650486182091</v>
@@ -4059,7 +4059,7 @@
         <v>-0.04747400421904999</v>
       </c>
       <c r="P20">
-        <v>-0.2138185309876257</v>
+        <v>0.08771942771483031</v>
       </c>
       <c r="Q20">
         <v>0.3988415319443278</v>
@@ -4083,10 +4083,10 @@
         <v>1</v>
       </c>
       <c r="X20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="b">
         <v>0</v>
@@ -4122,7 +4122,7 @@
         <v>0.2128269708712873</v>
       </c>
       <c r="AK20">
-        <v>0.379171497639863</v>
+        <v>0.077633538937407</v>
       </c>
       <c r="AL20">
         <v>-0.2334885652920905</v>
@@ -4137,7 +4137,7 @@
         <v>-0.06479752089293134</v>
       </c>
       <c r="AP20">
-        <v>-0.2311420476615071</v>
+        <v>0.07039591104094896</v>
       </c>
       <c r="AQ20">
         <v>0.3815180152704465</v>
@@ -4161,10 +4161,10 @@
         <v>0.9826764833261187</v>
       </c>
       <c r="AX20">
-        <v>0.9826764833261187</v>
+        <v>-0.01732351667388135</v>
       </c>
       <c r="AY20">
-        <v>0.9826764833261187</v>
+        <v>-0.01732351667388135</v>
       </c>
       <c r="AZ20">
         <v>-0.01732351667388135</v>
@@ -4208,7 +4208,7 @@
         <v>0.601318885903152</v>
       </c>
       <c r="E21">
-        <v>0.3953020579267524</v>
+        <v>0.1844683999603099</v>
       </c>
       <c r="F21">
         <v>0.01732351667388135</v>
@@ -4226,7 +4226,7 @@
         <v>0.1769662401943143</v>
       </c>
       <c r="K21">
-        <v>-0.0290505877820853</v>
+        <v>-0.2398842457485278</v>
       </c>
       <c r="L21">
         <v>-0.4070291290349564</v>
@@ -4241,7 +4241,7 @@
         <v>-0.5013188859031577</v>
       </c>
       <c r="P21">
-        <v>-0.2953020579267581</v>
+        <v>-0.08446839996031558</v>
       </c>
       <c r="Q21">
         <v>0.08267648332611297</v>
@@ -4304,7 +4304,7 @@
         <v>-0.2473864055145234</v>
       </c>
       <c r="AK21">
-        <v>-0.453403233490923</v>
+        <v>-0.6642368914573655</v>
       </c>
       <c r="AL21">
         <v>-0.831381774743794</v>
@@ -4319,7 +4319,7 @@
         <v>-0.9256715316119953</v>
       </c>
       <c r="AP21">
-        <v>-0.7196547036355958</v>
+        <v>-0.5088210456691533</v>
       </c>
       <c r="AQ21">
         <v>-0.3416761623827247</v>
@@ -4390,7 +4390,7 @@
         <v>-0.302587196304716</v>
       </c>
       <c r="E22">
-        <v>0.4494494662203161</v>
+        <v>0.3627307324263691</v>
       </c>
       <c r="F22">
         <v>0.4243526457088377</v>
@@ -4408,7 +4408,7 @@
         <v>-0.2278976248361338</v>
       </c>
       <c r="K22">
-        <v>0.5241390376888982</v>
+        <v>0.4374203038949512</v>
       </c>
       <c r="L22">
         <v>0.4990422171774198</v>
@@ -4423,7 +4423,7 @@
         <v>0.202587196304716</v>
       </c>
       <c r="P22">
-        <v>-0.5494494662203161</v>
+        <v>-0.4627307324263691</v>
       </c>
       <c r="Q22">
         <v>-0.5243526457088377</v>
@@ -4486,7 +4486,7 @@
         <v>-0.1532080533675517</v>
       </c>
       <c r="AK22">
-        <v>0.5988286091574804</v>
+        <v>0.5121098753635334</v>
       </c>
       <c r="AL22">
         <v>0.5737317886460019</v>
@@ -4501,7 +4501,7 @@
         <v>0.2772767677732981</v>
       </c>
       <c r="AP22">
-        <v>-0.474759894751734</v>
+        <v>-0.388041160957787</v>
       </c>
       <c r="AQ22">
         <v>-0.4496630742402555</v>
@@ -4572,7 +4572,7 @@
         <v>0.235914458649045</v>
       </c>
       <c r="E23">
-        <v>0.429419799243115</v>
+        <v>0.1794263626245832</v>
       </c>
       <c r="F23">
         <v>-0.07468957146858211</v>
@@ -4590,7 +4590,7 @@
         <v>0.1517551169621146</v>
       </c>
       <c r="K23">
-        <v>0.3452604575561846</v>
+        <v>0.09526702093765275</v>
       </c>
       <c r="L23">
         <v>-0.1588489131555126</v>
@@ -4605,7 +4605,7 @@
         <v>-0.3359144586490393</v>
       </c>
       <c r="P23">
-        <v>-0.5294197992431093</v>
+        <v>-0.2794263626245775</v>
       </c>
       <c r="Q23">
         <v>-0.0253104285314122</v>
@@ -4632,7 +4632,7 @@
         <v>1</v>
       </c>
       <c r="Y23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="b">
         <v>0</v>
@@ -4668,7 +4668,7 @@
         <v>0.06759577527518414</v>
       </c>
       <c r="AK23">
-        <v>0.2611011158692541</v>
+        <v>0.01110767925072231</v>
       </c>
       <c r="AL23">
         <v>-0.243008254842443</v>
@@ -4683,7 +4683,7 @@
         <v>-0.4200738003359698</v>
       </c>
       <c r="AP23">
-        <v>-0.6135791409300397</v>
+        <v>-0.363585704311508</v>
       </c>
       <c r="AQ23">
         <v>-0.1094697702183426</v>
@@ -4710,7 +4710,7 @@
         <v>0.9158406583130696</v>
       </c>
       <c r="AY23">
-        <v>0.9158406583130696</v>
+        <v>-0.08415934168693044</v>
       </c>
       <c r="AZ23">
         <v>-0.08415934168693044</v>
@@ -4754,7 +4754,7 @@
         <v>0.024124257856421</v>
       </c>
       <c r="E24">
-        <v>0.3825808826190411</v>
+        <v>0.1814061084957765</v>
       </c>
       <c r="F24">
         <v>0.08415934168693044</v>
@@ -4772,7 +4772,7 @@
         <v>-0.00387126286026539</v>
       </c>
       <c r="K24">
-        <v>0.3545853619023547</v>
+        <v>0.1534105877790901</v>
       </c>
       <c r="L24">
         <v>0.05616382097024405</v>
@@ -4787,7 +4787,7 @@
         <v>0.05587574214361993</v>
       </c>
       <c r="P24">
-        <v>-0.3025808826190002</v>
+        <v>-0.1014061084957356</v>
       </c>
       <c r="Q24">
         <v>-0.004159341686889514</v>
@@ -4850,7 +4850,7 @@
         <v>-0.03186678357695178</v>
       </c>
       <c r="AK24">
-        <v>0.3265898411856684</v>
+        <v>0.1254150670624037</v>
       </c>
       <c r="AL24">
         <v>0.02816830025355766</v>
@@ -4865,7 +4865,7 @@
         <v>0.02788022142693354</v>
       </c>
       <c r="AP24">
-        <v>-0.3305764033356866</v>
+        <v>-0.129401629212422</v>
       </c>
       <c r="AQ24">
         <v>-0.0321548624035759</v>
@@ -4936,7 +4936,7 @@
         <v>0.7155752359999999</v>
       </c>
       <c r="E25">
-        <v>0.4158212270970915</v>
+        <v>0.1900831754885381</v>
       </c>
       <c r="F25">
         <v>0.02799552071668639</v>
@@ -4954,7 +4954,7 @@
         <v>2.937382554894706</v>
       </c>
       <c r="K25">
-        <v>2.637628545991797</v>
+        <v>2.411890494383244</v>
       </c>
       <c r="L25">
         <v>2.249802839611392</v>
@@ -4969,7 +4969,7 @@
         <v>-0.6155752360000056</v>
       </c>
       <c r="P25">
-        <v>-0.3158212270970972</v>
+        <v>-0.09008317548854378</v>
       </c>
       <c r="Q25">
         <v>0.07200447928330793</v>
@@ -5032,7 +5032,7 @@
         <v>5.159189873789412</v>
       </c>
       <c r="AK25">
-        <v>4.859435864886503</v>
+        <v>4.63369781327795</v>
       </c>
       <c r="AL25">
         <v>4.471610158506098</v>
@@ -5047,7 +5047,7 @@
         <v>1.6062320828947</v>
       </c>
       <c r="AP25">
-        <v>1.905986091797609</v>
+        <v>2.131724143406162</v>
       </c>
       <c r="AQ25">
         <v>2.293811798178014</v>
@@ -5118,7 +5118,7 @@
         <v>-7.451780981</v>
       </c>
       <c r="E26">
-        <v>0.1862656172266596</v>
+        <v>-0.6845717329199352</v>
       </c>
       <c r="F26">
         <v>-2.221807318894706</v>
@@ -5136,7 +5136,7 @@
         <v>2.239176668751999</v>
       </c>
       <c r="K26">
-        <v>9.877223266978659</v>
+        <v>9.006385916832064</v>
       </c>
       <c r="L26">
         <v>7.469150330857293</v>
@@ -5151,7 +5151,7 @@
         <v>-4.448219019000001</v>
       </c>
       <c r="P26">
-        <v>-12.08626561722666</v>
+        <v>-11.21542826708007</v>
       </c>
       <c r="Q26">
         <v>-9.678192681105294</v>
@@ -5214,7 +5214,7 @@
         <v>11.930134318504</v>
       </c>
       <c r="AK26">
-        <v>19.56818091673066</v>
+        <v>18.69734356658406</v>
       </c>
       <c r="AL26">
         <v>17.16010798060929</v>
@@ -5229,7 +5229,7 @@
         <v>5.242738630751998</v>
       </c>
       <c r="AP26">
-        <v>-2.395307967474661</v>
+        <v>-1.524470617328067</v>
       </c>
       <c r="AQ26">
         <v>0.01276496864670484</v>
@@ -5300,7 +5300,7 @@
         <v>6.405694238</v>
       </c>
       <c r="E27">
-        <v>-1.982134026001563</v>
+        <v>-7.463655357282573</v>
       </c>
       <c r="F27">
         <v>-9.690957649751999</v>
@@ -5318,7 +5318,7 @@
         <v>-2.07460991238547</v>
       </c>
       <c r="K27">
-        <v>-10.46243817638703</v>
+        <v>-15.94395950766804</v>
       </c>
       <c r="L27">
         <v>-18.17126180013747</v>
@@ -5333,7 +5333,7 @@
         <v>0.2343057620000009</v>
       </c>
       <c r="P27">
-        <v>8.622134026001564</v>
+        <v>14.10365535728257</v>
       </c>
       <c r="Q27">
         <v>16.330957649752</v>
@@ -5396,7 +5396,7 @@
         <v>-10.55491406277094</v>
       </c>
       <c r="AK27">
-        <v>-18.9427423267725</v>
+        <v>-24.42426365805351</v>
       </c>
       <c r="AL27">
         <v>-26.65156595052294</v>
@@ -5411,7 +5411,7 @@
         <v>-8.24599838838547</v>
       </c>
       <c r="AP27">
-        <v>0.1418298756160947</v>
+        <v>5.623351206897103</v>
       </c>
       <c r="AQ27">
         <v>7.850653499366532</v>
@@ -5482,7 +5482,7 @@
         <v>-1.14456628109437</v>
       </c>
       <c r="E28">
-        <v>-1.488840052368066</v>
+        <v>-4.144592182330832</v>
       </c>
       <c r="F28">
         <v>8.48030415038547</v>
@@ -5500,7 +5500,7 @@
         <v>-1.48519888450069</v>
       </c>
       <c r="K28">
-        <v>-1.829472655774387</v>
+        <v>-4.485224785737152</v>
       </c>
       <c r="L28">
         <v>8.13967154697915</v>
@@ -5515,7 +5515,7 @@
         <v>0.7445662810943643</v>
       </c>
       <c r="P28">
-        <v>1.08884005236806</v>
+        <v>3.744592182330826</v>
       </c>
       <c r="Q28">
         <v>-8.880304150385475</v>
@@ -5578,7 +5578,7 @@
         <v>-1.825831487907011</v>
       </c>
       <c r="AK28">
-        <v>-2.170105259180707</v>
+        <v>-4.825857389143473</v>
       </c>
       <c r="AL28">
         <v>7.799038943572829</v>
@@ -5593,7 +5593,7 @@
         <v>0.4039336776880438</v>
       </c>
       <c r="AP28">
-        <v>0.7482074489617399</v>
+        <v>3.403959578924505</v>
       </c>
       <c r="AQ28">
         <v>-9.220936753791795</v>
@@ -5664,7 +5664,7 @@
         <v>1.297172517</v>
       </c>
       <c r="E29">
-        <v>0.4888170872567604</v>
+        <v>-0.8877061776737167</v>
       </c>
       <c r="F29">
         <v>0.3406326034063205</v>
@@ -5682,7 +5682,7 @@
         <v>3.104110385393072</v>
       </c>
       <c r="K29">
-        <v>2.295754955649832</v>
+        <v>0.9192316907193552</v>
       </c>
       <c r="L29">
         <v>2.147570471799392</v>
@@ -5697,7 +5697,7 @@
         <v>-2.006652516999999</v>
       </c>
       <c r="P29">
-        <v>-1.19829708725676</v>
+        <v>0.1782261776737175</v>
       </c>
       <c r="Q29">
         <v>-1.05011260340632</v>
@@ -5721,10 +5721,10 @@
         <v>1</v>
       </c>
       <c r="X29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="b">
         <v>1</v>
@@ -5760,7 +5760,7 @@
         <v>4.911048253786143</v>
       </c>
       <c r="AK29">
-        <v>4.102692824042904</v>
+        <v>2.726169559112427</v>
       </c>
       <c r="AL29">
         <v>3.954508340192464</v>
@@ -5775,7 +5775,7 @@
         <v>-0.1997146486069272</v>
       </c>
       <c r="AP29">
-        <v>0.6086407811363124</v>
+        <v>1.985164046066789</v>
       </c>
       <c r="AQ29">
         <v>0.7568252649867522</v>
@@ -5799,10 +5799,10 @@
         <v>2.806937868393072</v>
       </c>
       <c r="AX29">
-        <v>2.806937868393072</v>
+        <v>1.806937868393072</v>
       </c>
       <c r="AY29">
-        <v>2.806937868393072</v>
+        <v>1.806937868393072</v>
       </c>
       <c r="AZ29">
         <v>2.806937868393072</v>
@@ -5846,7 +5846,7 @@
         <v>0.673905569079516</v>
       </c>
       <c r="E30">
-        <v>0.731431855473491</v>
+        <v>0.892999978012982</v>
       </c>
       <c r="F30">
         <v>-1.806937868393072</v>
@@ -5864,7 +5864,7 @@
         <v>-0.959186549050742</v>
       </c>
       <c r="K30">
-        <v>-0.901660262656767</v>
+        <v>-0.740092140117276</v>
       </c>
       <c r="L30">
         <v>-3.44002998652333</v>
@@ -5879,7 +5879,7 @@
         <v>0.6360944309205</v>
       </c>
       <c r="P30">
-        <v>0.5785681445265251</v>
+        <v>0.417000021987034</v>
       </c>
       <c r="Q30">
         <v>3.116937868393088</v>
@@ -5942,7 +5942,7 @@
         <v>-2.592278667181</v>
       </c>
       <c r="AK30">
-        <v>-2.534752380787025</v>
+        <v>-2.373184258247534</v>
       </c>
       <c r="AL30">
         <v>-5.073122104653588</v>
@@ -5957,7 +5957,7 @@
         <v>-0.996997687209758</v>
       </c>
       <c r="AP30">
-        <v>-1.054523973603733</v>
+        <v>-1.216092096143224</v>
       </c>
       <c r="AQ30">
         <v>1.48384575026283</v>
@@ -6028,7 +6028,7 @@
         <v>0.347602564</v>
       </c>
       <c r="E31">
-        <v>0.4393764117943757</v>
+        <v>0.464029186385135</v>
       </c>
       <c r="F31">
         <v>1.633092118130258</v>
@@ -6046,7 +6046,7 @@
         <v>-1.346663732544459</v>
       </c>
       <c r="K31">
-        <v>-1.254889884750083</v>
+        <v>-1.230237110159324</v>
       </c>
       <c r="L31">
         <v>-0.06117417841420103</v>
@@ -6061,7 +6061,7 @@
         <v>1.17239743600001</v>
       </c>
       <c r="P31">
-        <v>1.080623588205634</v>
+        <v>1.055970813614875</v>
       </c>
       <c r="Q31">
         <v>-0.113092118130248</v>
@@ -6124,7 +6124,7 @@
         <v>-3.040930029088918</v>
       </c>
       <c r="AK31">
-        <v>-2.949156181294542</v>
+        <v>-2.924503406703783</v>
       </c>
       <c r="AL31">
         <v>-1.75544047495866</v>
@@ -6139,7 +6139,7 @@
         <v>-0.521868860544449</v>
       </c>
       <c r="AP31">
-        <v>-0.6136427083388247</v>
+        <v>-0.6382954829295842</v>
       </c>
       <c r="AQ31">
         <v>-1.807358414674707</v>
@@ -6210,7 +6210,7 @@
         <v>-0.24627924</v>
       </c>
       <c r="E32">
-        <v>0.1639891127141883</v>
+        <v>-0.6356350162097709</v>
       </c>
       <c r="F32">
         <v>1.694266296544459</v>
@@ -6228,7 +6228,7 @@
         <v>0.1009104006117954</v>
       </c>
       <c r="K32">
-        <v>0.5111787533259837</v>
+        <v>-0.2884453755979755</v>
       </c>
       <c r="L32">
         <v>2.041455937156254</v>
@@ -6243,7 +6243,7 @@
         <v>-0.293720759999992</v>
       </c>
       <c r="P32">
-        <v>-0.7039891127141804</v>
+        <v>0.09563501620977888</v>
       </c>
       <c r="Q32">
         <v>-2.234266296544451</v>
@@ -6264,10 +6264,10 @@
         <v>0</v>
       </c>
       <c r="W32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="b">
         <v>1</v>
@@ -6306,7 +6306,7 @@
         <v>0.4481000412235908</v>
       </c>
       <c r="AK32">
-        <v>0.8583683939377791</v>
+        <v>0.05874426501381991</v>
       </c>
       <c r="AL32">
         <v>2.38864557776805</v>
@@ -6321,7 +6321,7 @@
         <v>0.05346888061180338</v>
       </c>
       <c r="AP32">
-        <v>-0.356799472102385</v>
+        <v>0.4428246568215743</v>
       </c>
       <c r="AQ32">
         <v>-1.887076655932656</v>
@@ -6342,10 +6342,10 @@
         <v>0.3471896406117954</v>
       </c>
       <c r="AW32">
-        <v>1.347189640611795</v>
+        <v>0.3471896406117954</v>
       </c>
       <c r="AX32">
-        <v>1.347189640611795</v>
+        <v>0.3471896406117954</v>
       </c>
       <c r="AY32">
         <v>1.347189640611795</v>
@@ -6392,7 +6392,7 @@
         <v>2.276288116</v>
       </c>
       <c r="E33">
-        <v>0.497856732295311</v>
+        <v>0.3241408423207837</v>
       </c>
       <c r="F33">
         <v>-0.3471896406117954</v>
@@ -6410,7 +6410,7 @@
         <v>2.040883219578154</v>
       </c>
       <c r="K33">
-        <v>0.2624518358734654</v>
+        <v>0.08873594589893813</v>
       </c>
       <c r="L33">
         <v>-0.5825945370336409</v>
@@ -6425,7 +6425,7 @@
         <v>-1.811002568089656</v>
       </c>
       <c r="P33">
-        <v>-0.03257118438496753</v>
+        <v>0.1411447055895598</v>
       </c>
       <c r="Q33">
         <v>0.8124751885221388</v>
@@ -6449,10 +6449,10 @@
         <v>1</v>
       </c>
       <c r="X33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="b">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>1.805478323156309</v>
       </c>
       <c r="AK33">
-        <v>0.02704693945161984</v>
+        <v>-0.1466689505229075</v>
       </c>
       <c r="AL33">
         <v>-0.8179994334554865</v>
@@ -6503,7 +6503,7 @@
         <v>-2.046407464511502</v>
       </c>
       <c r="AP33">
-        <v>-0.2679760808068131</v>
+        <v>-0.09426019083228582</v>
       </c>
       <c r="AQ33">
         <v>0.5770702921002933</v>
@@ -6527,10 +6527,10 @@
         <v>0.7645951035781544</v>
       </c>
       <c r="AX33">
-        <v>0.7645951035781544</v>
+        <v>-0.2354048964218456</v>
       </c>
       <c r="AY33">
-        <v>0.7645951035781544</v>
+        <v>-0.2354048964218456</v>
       </c>
       <c r="AZ33">
         <v>-0.2354048964218456</v>
@@ -6574,7 +6574,7 @@
         <v>0.92820296</v>
       </c>
       <c r="E34">
-        <v>0.5496377906332163</v>
+        <v>0.6660072552246967</v>
       </c>
       <c r="F34">
         <v>0.2354048964218456</v>
@@ -6592,7 +6592,7 @@
         <v>0.7884731043875122</v>
       </c>
       <c r="K34">
-        <v>0.4099079350207285</v>
+        <v>0.526277399612209</v>
       </c>
       <c r="L34">
         <v>0.09567504080935779</v>
@@ -6607,7 +6607,7 @@
         <v>-0.54820296</v>
       </c>
       <c r="P34">
-        <v>-0.1696377906332163</v>
+        <v>-0.2860072552246967</v>
       </c>
       <c r="Q34">
         <v>0.1445951035781544</v>
@@ -6670,7 +6670,7 @@
         <v>0.6487432487750244</v>
       </c>
       <c r="AK34">
-        <v>0.2701780794082407</v>
+        <v>0.3865475439997212</v>
       </c>
       <c r="AL34">
         <v>-0.04405481480313</v>
@@ -6685,7 +6685,7 @@
         <v>-0.6879328156124878</v>
       </c>
       <c r="AP34">
-        <v>-0.3093676462457041</v>
+        <v>-0.4257371108371845</v>
       </c>
       <c r="AQ34">
         <v>0.004865247965666619</v>
@@ -6756,7 +6756,7 @@
         <v>-0.277926312</v>
       </c>
       <c r="E35">
-        <v>0.4929156585266765</v>
+        <v>0.3437767272872988</v>
       </c>
       <c r="F35">
         <v>0.1397298556124878</v>
@@ -6774,7 +6774,7 @@
         <v>-0.6780752046112106</v>
       </c>
       <c r="K35">
-        <v>0.0927667659154659</v>
+        <v>-0.05637216532391182</v>
       </c>
       <c r="L35">
         <v>-0.2604190369987228</v>
@@ -6789,7 +6789,7 @@
         <v>0.317926312</v>
       </c>
       <c r="P35">
-        <v>-0.4529156585266765</v>
+        <v>-0.3037767272872988</v>
       </c>
       <c r="Q35">
         <v>-0.09972985561248779</v>
@@ -6810,7 +6810,7 @@
         <v>1</v>
       </c>
       <c r="W35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="b">
         <v>1</v>
@@ -6852,7 +6852,7 @@
         <v>-1.078224097222421</v>
       </c>
       <c r="AK35">
-        <v>-0.3073821266957447</v>
+        <v>-0.4565210579351224</v>
       </c>
       <c r="AL35">
         <v>-0.6605679296099334</v>
@@ -6867,7 +6867,7 @@
         <v>-0.08222258061121063</v>
       </c>
       <c r="AP35">
-        <v>-0.8530645511378872</v>
+        <v>-0.7039256198985094</v>
       </c>
       <c r="AQ35">
         <v>-0.4998787482236984</v>
@@ -6888,7 +6888,7 @@
         <v>0.5998511073887893</v>
       </c>
       <c r="AW35">
-        <v>0.5998511073887893</v>
+        <v>-0.4001488926112106</v>
       </c>
       <c r="AX35">
         <v>0.5998511073887893</v>
@@ -6938,7 +6938,7 @@
         <v>0.251316528</v>
       </c>
       <c r="E36">
-        <v>0.4910150553647586</v>
+        <v>0.4120709423816584</v>
       </c>
       <c r="F36">
         <v>0.4001488926112106</v>
@@ -6956,7 +6956,7 @@
         <v>0.6866226315472805</v>
       </c>
       <c r="K36">
-        <v>0.9263211589120393</v>
+        <v>0.847377045928939</v>
       </c>
       <c r="L36">
         <v>0.8354549961584912</v>
@@ -6971,7 +6971,7 @@
         <v>-0.541316528</v>
       </c>
       <c r="P36">
-        <v>-0.7810150553647586</v>
+        <v>-0.7020709423816585</v>
       </c>
       <c r="Q36">
         <v>-0.6901488926112106</v>
@@ -7034,7 +7034,7 @@
         <v>1.121928735094561</v>
       </c>
       <c r="AK36">
-        <v>1.36162726245932</v>
+        <v>1.28268314947622</v>
       </c>
       <c r="AL36">
         <v>1.270761099705772</v>
@@ -7049,7 +7049,7 @@
         <v>-0.1060104244527194</v>
       </c>
       <c r="AP36">
-        <v>-0.345708951817478</v>
+        <v>-0.2667648388343778</v>
       </c>
       <c r="AQ36">
         <v>-0.25484278906393</v>
@@ -7120,7 +7120,7 @@
         <v>0.538736913</v>
       </c>
       <c r="E37">
-        <v>0.5994482967366578</v>
+        <v>0.6519408127754134</v>
       </c>
       <c r="F37">
         <v>-0.4353061035472806</v>
@@ -7138,7 +7138,7 @@
         <v>0.8739636566446591</v>
       </c>
       <c r="K37">
-        <v>0.9346750403813169</v>
+        <v>0.9871675564200725</v>
       </c>
       <c r="L37">
         <v>-0.1000793599026215</v>
@@ -7153,7 +7153,7 @@
         <v>-0.7466148704152918</v>
       </c>
       <c r="P37">
-        <v>-0.8073262541519496</v>
+        <v>-0.8598187701907052</v>
       </c>
       <c r="Q37">
         <v>0.2274281461319888</v>
@@ -7216,7 +7216,7 @@
         <v>1.209190400289318</v>
       </c>
       <c r="AK37">
-        <v>1.269901784025976</v>
+        <v>1.322394300064732</v>
       </c>
       <c r="AL37">
         <v>0.2351473837420376</v>
@@ -7231,7 +7231,7 @@
         <v>-0.4113881267706327</v>
       </c>
       <c r="AP37">
-        <v>-0.4720995105072905</v>
+        <v>-0.5245920265460461</v>
       </c>
       <c r="AQ37">
         <v>0.5626548897766479</v>
@@ -7302,7 +7302,7 @@
         <v>-0.318864405</v>
       </c>
       <c r="E38">
-        <v>0.6333318196243403</v>
+        <v>0.8814549586592991</v>
       </c>
       <c r="F38">
         <v>-0.3352267436446591</v>
@@ -7320,7 +7320,7 @@
         <v>-0.3374241674350372</v>
       </c>
       <c r="K38">
-        <v>0.6147720571893032</v>
+        <v>0.862895196224262</v>
       </c>
       <c r="L38">
         <v>-0.3537865060796963</v>
@@ -7335,7 +7335,7 @@
         <v>0.4395122381785803</v>
       </c>
       <c r="P38">
-        <v>-0.51268398644576</v>
+        <v>-0.7608071254807188</v>
       </c>
       <c r="Q38">
         <v>0.4558745768232394</v>
@@ -7398,7 +7398,7 @@
         <v>-0.3559839298700743</v>
       </c>
       <c r="AK38">
-        <v>0.5962122947542661</v>
+        <v>0.8443354337892249</v>
       </c>
       <c r="AL38">
         <v>-0.3723462685147334</v>
@@ -7413,7 +7413,7 @@
         <v>0.4209524757435432</v>
       </c>
       <c r="AP38">
-        <v>-0.5312437488807971</v>
+        <v>-0.7793668879157559</v>
       </c>
       <c r="AQ38">
         <v>0.4373148143882022</v>
@@ -7484,7 +7484,7 @@
         <v>-0.474503149</v>
       </c>
       <c r="E39">
-        <v>0.5452363198887364</v>
+        <v>0.5350086232236873</v>
       </c>
       <c r="F39">
         <v>0.01855976243503714</v>
@@ -7502,7 +7502,7 @@
         <v>-0.3448855210025918</v>
       </c>
       <c r="K39">
-        <v>0.6748539478861446</v>
+        <v>0.6646262512210954</v>
       </c>
       <c r="L39">
         <v>0.1481773904324453</v>
@@ -7517,7 +7517,7 @@
         <v>0.294503149</v>
       </c>
       <c r="P39">
-        <v>-0.7252363198887364</v>
+        <v>-0.7150086232236872</v>
       </c>
       <c r="Q39">
         <v>-0.1985597624350371</v>
@@ -7580,7 +7580,7 @@
         <v>-0.2152678930051836</v>
       </c>
       <c r="AK39">
-        <v>0.8044715758835528</v>
+        <v>0.7942438792185036</v>
       </c>
       <c r="AL39">
         <v>0.2777950184298535</v>
@@ -7595,7 +7595,7 @@
         <v>0.4241207769974082</v>
       </c>
       <c r="AP39">
-        <v>-0.5956186918913282</v>
+        <v>-0.585390995226279</v>
       </c>
       <c r="AQ39">
         <v>-0.06894213443762895</v>
@@ -7666,7 +7666,7 @@
         <v>-0.290614742754258</v>
       </c>
       <c r="E40">
-        <v>0.5509988879663087</v>
+        <v>0.5007400141027678</v>
       </c>
       <c r="F40">
         <v>-0.1296176279974082</v>
@@ -7684,7 +7684,7 @@
         <v>-0.003551125752694839</v>
       </c>
       <c r="K40">
-        <v>0.8380625049678718</v>
+        <v>0.787803631104331</v>
       </c>
       <c r="L40">
         <v>0.157445989004155</v>
@@ -7699,7 +7699,7 @@
         <v>0.334614742754258</v>
       </c>
       <c r="P40">
-        <v>-0.5069988879663087</v>
+        <v>-0.4567400141027678</v>
       </c>
       <c r="Q40">
         <v>0.1736176279974082</v>
@@ -7762,7 +7762,7 @@
         <v>0.2835124912488683</v>
       </c>
       <c r="AK40">
-        <v>1.125126121969435</v>
+        <v>1.074867248105894</v>
       </c>
       <c r="AL40">
         <v>0.4445096060057182</v>
@@ -7777,7 +7777,7 @@
         <v>0.6216783597558212</v>
       </c>
       <c r="AP40">
-        <v>-0.2199352709647455</v>
+        <v>-0.1696763971012046</v>
       </c>
       <c r="AQ40">
         <v>0.4606812449989714</v>
@@ -7848,7 +7848,7 @@
         <v>-0.236658442</v>
       </c>
       <c r="E41">
-        <v>0.5767737563214386</v>
+        <v>0.6148977852456914</v>
       </c>
       <c r="F41">
         <v>-0.2870636170015632</v>
@@ -7866,7 +7866,7 @@
         <v>-0.4502542815245076</v>
       </c>
       <c r="K41">
-        <v>0.363177916796931</v>
+        <v>0.4013019457211838</v>
       </c>
       <c r="L41">
         <v>-0.5006594565260708</v>
@@ -7881,7 +7881,7 @@
         <v>0.1541484015364963</v>
       </c>
       <c r="P41">
-        <v>-0.6592837967849423</v>
+        <v>-0.6974078257091951</v>
       </c>
       <c r="Q41">
         <v>0.2045535765380594</v>
@@ -7944,7 +7944,7 @@
         <v>-0.6638501210490153</v>
       </c>
       <c r="AK41">
-        <v>0.1495820772724233</v>
+        <v>0.1877061061966762</v>
       </c>
       <c r="AL41">
         <v>-0.7142552960505784</v>
@@ -7959,7 +7959,7 @@
         <v>-0.05944743798801136</v>
       </c>
       <c r="AP41">
-        <v>-0.87287963630945</v>
+        <v>-0.9110036652337028</v>
       </c>
       <c r="AQ41">
         <v>-0.009042262986448169</v>
@@ -8030,7 +8030,7 @@
         <v>0.374912587</v>
       </c>
       <c r="E42">
-        <v>0.5308012840444406</v>
+        <v>0.5461074682008229</v>
       </c>
       <c r="F42">
         <v>0.2135958395245076</v>
@@ -8048,7 +8048,7 @@
         <v>0.4416746280109616</v>
       </c>
       <c r="K42">
-        <v>0.5975633250554021</v>
+        <v>0.6128695092117844</v>
       </c>
       <c r="L42">
         <v>0.2803578805354692</v>
@@ -8063,7 +8063,7 @@
         <v>-0.1166600650424698</v>
       </c>
       <c r="P42">
-        <v>-0.2725487620869104</v>
+        <v>-0.2878549462432927</v>
       </c>
       <c r="Q42">
         <v>0.04465668243302257</v>
@@ -8126,7 +8126,7 @@
         <v>0.5084366690219231</v>
       </c>
       <c r="AK42">
-        <v>0.6643253660663636</v>
+        <v>0.6796315502227459</v>
       </c>
       <c r="AL42">
         <v>0.3471199215464307</v>
@@ -8141,7 +8141,7 @@
         <v>-0.0498980240315083</v>
       </c>
       <c r="AP42">
-        <v>-0.2057867210759489</v>
+        <v>-0.2210929052323312</v>
       </c>
       <c r="AQ42">
         <v>0.1114187234439841</v>
@@ -8212,7 +8212,7 @@
         <v>-0.559269386</v>
       </c>
       <c r="E43">
-        <v>0.5192370550060136</v>
+        <v>0.3984361203848173</v>
       </c>
       <c r="F43">
         <v>-0.06676204101096155</v>
@@ -8230,7 +8230,7 @@
         <v>-0.66448220283405</v>
       </c>
       <c r="K43">
-        <v>0.4140242381719635</v>
+        <v>0.2932233035507672</v>
       </c>
       <c r="L43">
         <v>-0.1719748578450117</v>
@@ -8245,7 +8245,7 @@
         <v>0.5120938607750563</v>
       </c>
       <c r="P43">
-        <v>-0.5664125802309573</v>
+        <v>-0.445611645609761</v>
       </c>
       <c r="Q43">
         <v>0.01958651578601781</v>
@@ -8308,7 +8308,7 @@
         <v>-0.7696950196681001</v>
       </c>
       <c r="AK43">
-        <v>0.3088114213379134</v>
+        <v>0.1880104867167171</v>
       </c>
       <c r="AL43">
         <v>-0.2771876746790617</v>
@@ -8323,7 +8323,7 @@
         <v>0.4068810439410062</v>
       </c>
       <c r="AP43">
-        <v>-0.6716253970650075</v>
+        <v>-0.5508244624438111</v>
       </c>
       <c r="AQ43">
         <v>-0.08562630104803229</v>
@@ -8394,7 +8394,7 @@
         <v>0.135411462</v>
       </c>
       <c r="E44">
-        <v>0.5206063595951018</v>
+        <v>0.4733275747052469</v>
       </c>
       <c r="F44">
         <v>0.1052128168340501</v>
@@ -8412,7 +8412,7 @@
         <v>0.3360611849122814</v>
       </c>
       <c r="K44">
-        <v>0.7212560825073833</v>
+        <v>0.6739772976175282</v>
       </c>
       <c r="L44">
         <v>0.3058625397463315</v>
@@ -8427,7 +8427,7 @@
         <v>0.07881831854894769</v>
       </c>
       <c r="P44">
-        <v>-0.3063765790461541</v>
+        <v>-0.2590977941562992</v>
       </c>
       <c r="Q44">
         <v>0.1090169637148976</v>
@@ -8490,7 +8490,7 @@
         <v>0.5367109078245629</v>
       </c>
       <c r="AK44">
-        <v>0.9219058054196647</v>
+        <v>0.8746270205298097</v>
       </c>
       <c r="AL44">
         <v>0.5065122626586129</v>
@@ -8505,7 +8505,7 @@
         <v>0.2794680414612291</v>
       </c>
       <c r="AP44">
-        <v>-0.1057268561338727</v>
+        <v>-0.0584480712440178</v>
       </c>
       <c r="AQ44">
         <v>0.309666686627179</v>
@@ -8576,7 +8576,7 @@
         <v>0.332099825</v>
       </c>
       <c r="E45">
-        <v>0.531764550366899</v>
+        <v>0.4738675049177161</v>
       </c>
       <c r="F45">
         <v>-0.2006497229122814</v>
@@ -8594,7 +8594,7 @@
         <v>-0.07958040477500478</v>
       </c>
       <c r="K45">
-        <v>0.1200843205918942</v>
+        <v>0.06218727514271133</v>
       </c>
       <c r="L45">
         <v>-0.6123299526872862</v>
@@ -8609,7 +8609,7 @@
         <v>-0.09266266758538652</v>
       </c>
       <c r="P45">
-        <v>-0.2923273929522855</v>
+        <v>-0.2344303475031026</v>
       </c>
       <c r="Q45">
         <v>0.4400868803268949</v>
@@ -8672,7 +8672,7 @@
         <v>-0.4912606345500096</v>
       </c>
       <c r="AK45">
-        <v>-0.2915959091831106</v>
+        <v>-0.3494929546322935</v>
       </c>
       <c r="AL45">
         <v>-1.024010182462291</v>
@@ -8687,7 +8687,7 @@
         <v>-0.5043428973603913</v>
       </c>
       <c r="AP45">
-        <v>-0.7040076227272902</v>
+        <v>-0.6461105772781074</v>
       </c>
       <c r="AQ45">
         <v>0.02840665055189012</v>
@@ -8758,7 +8758,7 @@
         <v>0.028721274</v>
       </c>
       <c r="E46">
-        <v>0.4771990295558996</v>
+        <v>0.3519456421565676</v>
       </c>
       <c r="F46">
         <v>0.4116802297750048</v>
@@ -8776,7 +8776,7 @@
         <v>0.3054124294241067</v>
       </c>
       <c r="K46">
-        <v>0.7538901849800064</v>
+        <v>0.6286367975806744</v>
       </c>
       <c r="L46">
         <v>0.6883713851991116</v>
@@ -8791,7 +8791,7 @@
         <v>0.01845756018304325</v>
       </c>
       <c r="P46">
-        <v>-0.4300201953728564</v>
+        <v>-0.3047668079735243</v>
       </c>
       <c r="Q46">
         <v>-0.3645013955919615</v>
@@ -8854,7 +8854,7 @@
         <v>0.5821035848482135</v>
       </c>
       <c r="AK46">
-        <v>1.030581340404113</v>
+        <v>0.9053279530047811</v>
       </c>
       <c r="AL46">
         <v>0.9650625406232183</v>
@@ -8869,7 +8869,7 @@
         <v>0.2951487156071499</v>
       </c>
       <c r="AP46">
-        <v>-0.1533290399487496</v>
+        <v>-0.02807565254941763</v>
       </c>
       <c r="AQ46">
         <v>-0.08781024016785482</v>
@@ -8940,7 +8940,7 @@
         <v>0.042359665</v>
       </c>
       <c r="E47">
-        <v>0.5174406429343102</v>
+        <v>0.4328090033804217</v>
       </c>
       <c r="F47">
         <v>-0.2766911554241067</v>
@@ -8958,7 +8958,7 @@
         <v>0.042359665</v>
       </c>
       <c r="K47">
-        <v>0.5174406429343102</v>
+        <v>0.4328090033804217</v>
       </c>
       <c r="L47">
         <v>-0.2766911554241067</v>
@@ -8973,7 +8973,7 @@
         <v>0.0535898706205764</v>
       </c>
       <c r="P47">
-        <v>-0.4214911073137338</v>
+        <v>-0.3368594677598453</v>
       </c>
       <c r="Q47">
         <v>0.3726406910446831</v>
@@ -9036,7 +9036,7 @@
         <v>0.042359665</v>
       </c>
       <c r="AK47">
-        <v>0.5174406429343102</v>
+        <v>0.4328090033804217</v>
       </c>
       <c r="AL47">
         <v>-0.2766911554241067</v>
@@ -9051,7 +9051,7 @@
         <v>0.0535898706205764</v>
       </c>
       <c r="AP47">
-        <v>-0.4214911073137338</v>
+        <v>-0.3368594677598453</v>
       </c>
       <c r="AQ47">
         <v>0.3726406910446831</v>
